--- a/data/trans_dic/P23_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,26; 49,83</t>
+          <t>42,16; 50,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,66; 42,31</t>
+          <t>34,35; 42,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,51</t>
+          <t>33,58; 40,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,31; 26,83</t>
+          <t>20,35; 26,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 26,59</t>
+          <t>20,07; 26,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,97; 28,65</t>
+          <t>22,03; 28,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 37,41</t>
+          <t>32,34; 37,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,35; 33,55</t>
+          <t>28,33; 33,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,63; 33,98</t>
+          <t>28,33; 33,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,08; 45,54</t>
+          <t>38,89; 45,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 43,08</t>
+          <t>36,66; 43,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,47; 36,3</t>
+          <t>30,25; 36,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 26,14</t>
+          <t>20,72; 26,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,34; 31,05</t>
+          <t>25,17; 31,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,33; 29,05</t>
+          <t>23,44; 28,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,84; 35,22</t>
+          <t>30,81; 35,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,74; 36,07</t>
+          <t>31,85; 36,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,42; 31,61</t>
+          <t>27,5; 31,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,93; 41,4</t>
+          <t>33,8; 41,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,71; 45,53</t>
+          <t>37,91; 45,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,62; 45,16</t>
+          <t>37,1; 44,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 28,2</t>
+          <t>22,01; 28,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 33,54</t>
+          <t>26,13; 32,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 32,25</t>
+          <t>25,92; 32,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,52; 33,76</t>
+          <t>28,7; 33,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,78; 38,09</t>
+          <t>32,75; 37,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,43; 37,36</t>
+          <t>32,47; 37,67</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,17; 46,49</t>
+          <t>39,84; 46,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,37; 41,97</t>
+          <t>35,46; 41,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,54; 33,89</t>
+          <t>27,97; 34,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,59; 32,13</t>
+          <t>26,66; 32,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,26; 30,89</t>
+          <t>25,11; 30,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 27,64</t>
+          <t>22,03; 27,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,58; 37,97</t>
+          <t>33,76; 38,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,86; 35,19</t>
+          <t>30,94; 35,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,5; 29,48</t>
+          <t>25,44; 29,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,46; 44,04</t>
+          <t>40,59; 44,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,86; 41,33</t>
+          <t>37,88; 41,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,41; 36,82</t>
+          <t>33,38; 36,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,11; 27,19</t>
+          <t>24,15; 26,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,88; 28,93</t>
+          <t>25,92; 28,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,68; 27,64</t>
+          <t>24,63; 27,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,61; 34,98</t>
+          <t>32,56; 35,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,16; 34,63</t>
+          <t>32,26; 34,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 31,62</t>
+          <t>29,32; 31,6</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>293262; 345841</t>
+          <t>292564; 347821</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243855; 297606</t>
+          <t>241666; 297842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>225737; 273338</t>
+          <t>226604; 274142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139780; 184711</t>
+          <t>140079; 184670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>138243; 185378</t>
+          <t>139879; 186263</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147594; 192436</t>
+          <t>147982; 193579</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>447718; 517184</t>
+          <t>447062; 516602</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>397080; 469908</t>
+          <t>396699; 467375</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>385481; 457496</t>
+          <t>381436; 454408</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>375494; 437488</t>
+          <t>373616; 439900</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>372168; 438059</t>
+          <t>372841; 439126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311167; 370782</t>
+          <t>308944; 371510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198837; 253178</t>
+          <t>200682; 254330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>261603; 320443</t>
+          <t>259776; 321543</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>243123; 302717</t>
+          <t>244246; 300278</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>594892; 679527</t>
+          <t>594392; 677643</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>650333; 739020</t>
+          <t>652558; 743528</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>565869; 652277</t>
+          <t>567400; 651704</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>230192; 280930</t>
+          <t>229328; 281630</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>285721; 344951</t>
+          <t>287218; 342561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285451; 342623</t>
+          <t>281510; 338439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148437; 192863</t>
+          <t>150497; 195841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>205264; 260365</t>
+          <t>202796; 254893</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>197755; 252480</t>
+          <t>202924; 254572</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>388591; 459894</t>
+          <t>391018; 459703</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>502775; 584218</t>
+          <t>502382; 582649</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>499962; 575888</t>
+          <t>500489; 580755</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>378493; 438036</t>
+          <t>375409; 433560</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>335214; 397767</t>
+          <t>336096; 397070</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>258200; 317739</t>
+          <t>262270; 319350</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>276166; 333702</t>
+          <t>276920; 336028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>265440; 324672</t>
+          <t>263906; 324290</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>230990; 288153</t>
+          <t>229682; 286428</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>665141; 752175</t>
+          <t>668781; 754773</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>616867; 703414</t>
+          <t>618317; 703259</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>504909; 583757</t>
+          <t>503823; 584957</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1325414; 1442511</t>
+          <t>1329366; 1446641</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1296941; 1415781</t>
+          <t>1297780; 1415261</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1133536; 1249039</t>
+          <t>1132509; 1247052</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>814610; 918767</t>
+          <t>815961; 910974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>920492; 1029014</t>
+          <t>921956; 1029669</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>873361; 978159</t>
+          <t>871670; 977404</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2170312; 2328069</t>
+          <t>2166858; 2330261</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2245409; 2417827</t>
+          <t>2252453; 2413925</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2029989; 2191972</t>
+          <t>2032585; 2190225</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P23_R-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42,16; 50,12</t>
+          <t>42,37; 50,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,35; 42,34</t>
+          <t>34,86; 42,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,58; 40,63</t>
+          <t>33,34; 40,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 26,83</t>
+          <t>20,62; 26,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,07; 26,72</t>
+          <t>19,95; 26,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 28,82</t>
+          <t>21,97; 28,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,34; 37,37</t>
+          <t>32,14; 37,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,37</t>
+          <t>28,13; 33,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 33,75</t>
+          <t>28,47; 33,77</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,89; 45,79</t>
+          <t>38,71; 45,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,66; 43,18</t>
+          <t>36,8; 43,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 36,37</t>
+          <t>30,39; 36,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 26,26</t>
+          <t>20,54; 25,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,17; 31,15</t>
+          <t>25,34; 31,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,44; 28,82</t>
+          <t>23,22; 28,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,81; 35,13</t>
+          <t>30,59; 35,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,85; 36,29</t>
+          <t>31,84; 36,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,5; 31,58</t>
+          <t>27,58; 31,54</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,8; 41,51</t>
+          <t>33,58; 41,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,91; 45,22</t>
+          <t>37,76; 44,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,1; 44,61</t>
+          <t>37,58; 45,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,01; 28,64</t>
+          <t>22,01; 28,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 32,84</t>
+          <t>26,39; 33,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,92; 32,52</t>
+          <t>25,76; 32,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 33,74</t>
+          <t>28,59; 33,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,75; 37,99</t>
+          <t>33,07; 38,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,47; 37,67</t>
+          <t>32,58; 37,56</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,84; 46,01</t>
+          <t>39,89; 46,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,46; 41,9</t>
+          <t>35,37; 41,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,97; 34,06</t>
+          <t>27,75; 33,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,66; 32,35</t>
+          <t>26,4; 32,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,11; 30,86</t>
+          <t>25,01; 30,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,03; 27,48</t>
+          <t>22,09; 27,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,76; 38,1</t>
+          <t>33,87; 37,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,94; 35,19</t>
+          <t>30,74; 35,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 29,54</t>
+          <t>25,45; 29,46</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,59; 44,17</t>
+          <t>40,64; 44,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>37,88; 41,31</t>
+          <t>37,85; 41,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,38; 36,76</t>
+          <t>33,65; 36,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 26,96</t>
+          <t>24,13; 27,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,92; 28,95</t>
+          <t>25,88; 29,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,63; 27,62</t>
+          <t>24,63; 27,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,56; 35,02</t>
+          <t>32,66; 34,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,26; 34,57</t>
+          <t>32,27; 34,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,32; 31,6</t>
+          <t>29,35; 31,64</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>292564; 347821</t>
+          <t>294085; 347706</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>241666; 297842</t>
+          <t>245260; 298644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>226604; 274142</t>
+          <t>224999; 275259</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140079; 184670</t>
+          <t>141926; 184318</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>139879; 186263</t>
+          <t>139050; 187463</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>147982; 193579</t>
+          <t>147590; 192771</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>447062; 516602</t>
+          <t>444332; 516970</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396699; 467375</t>
+          <t>393956; 465300</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>381436; 454408</t>
+          <t>383405; 454703</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>373616; 439900</t>
+          <t>371898; 435767</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>372841; 439126</t>
+          <t>374223; 441099</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>308944; 371510</t>
+          <t>310393; 370178</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>200682; 254330</t>
+          <t>198869; 250804</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>259776; 321543</t>
+          <t>261558; 324483</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>244246; 300278</t>
+          <t>241982; 300105</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>594392; 677643</t>
+          <t>590162; 675784</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>652558; 743528</t>
+          <t>652427; 741023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>567400; 651704</t>
+          <t>569169; 650692</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>229328; 281630</t>
+          <t>227819; 280555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>287218; 342561</t>
+          <t>286103; 340681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>281510; 338439</t>
+          <t>285142; 341422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>150497; 195841</t>
+          <t>150521; 195218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>202796; 254893</t>
+          <t>204801; 261056</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>202924; 254572</t>
+          <t>201681; 252364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>391018; 459703</t>
+          <t>389477; 457456</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>502382; 582649</t>
+          <t>507170; 585346</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>500489; 580755</t>
+          <t>502215; 579090</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>375409; 433560</t>
+          <t>375854; 435213</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>336096; 397070</t>
+          <t>335213; 397455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>262270; 319350</t>
+          <t>260180; 316492</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>276920; 336028</t>
+          <t>274234; 334530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>263906; 324290</t>
+          <t>262785; 322803</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>229682; 286428</t>
+          <t>230295; 284468</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>668781; 754773</t>
+          <t>670828; 752181</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>618317; 703259</t>
+          <t>614330; 700019</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>503823; 584957</t>
+          <t>504002; 583241</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1329366; 1446641</t>
+          <t>1331274; 1442553</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1297780; 1415261</t>
+          <t>1296778; 1414730</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1132509; 1247052</t>
+          <t>1141425; 1252088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>815961; 910974</t>
+          <t>815438; 919173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>921956; 1029669</t>
+          <t>920335; 1033648</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>871670; 977404</t>
+          <t>871656; 984620</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2166858; 2330261</t>
+          <t>2173732; 2325182</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2252453; 2413925</t>
+          <t>2253291; 2411864</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2032585; 2190225</t>
+          <t>2034452; 2193205</t>
         </is>
       </c>
     </row>
